--- a/data/trans_orig/KIDMED_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R2-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3883</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1685</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5586</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1685</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6792</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59213</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56380</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>54922</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72922</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>69021</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74607</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,51%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>183</t>
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>144322</t>
+          <t>114136</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139215</t>
+          <t>111640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10116</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5665</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17590</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3933</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9830</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18683</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104835</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>97361</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109286</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>121716</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>115819</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>124409</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>115198</t>
+          <t>95372</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107740</t>
+          <t>90944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120443</t>
+          <t>97834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>236913</t>
+          <t>200206</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>227993</t>
+          <t>191847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>243040</t>
+          <t>205384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>642</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56658</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54142</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>54901</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52878</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>53470</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>50594</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>54112</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63782</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>59293</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>64633</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>184</t>
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>118683</t>
+          <t>110127</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115457</t>
+          <t>107546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4203</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10320</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>13192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67811</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63774</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>65479</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>59362</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>68113</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>73369</t>
+          <t>66017</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68230</t>
+          <t>60431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>68814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>138849</t>
+          <t>133828</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132074</t>
+          <t>127086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142528</t>
+          <t>137077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>138</t>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4058</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>46564</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>43151</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>91,4%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>42303</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>39376</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>43755</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>42198</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50147</t>
+          <t>39043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>95369</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92304</t>
+          <t>85144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97128</t>
+          <t>90576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,107 +2778,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7486</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14021</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5024</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2142</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10050</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>12779</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>7677</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>20716</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>4,87%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>12568</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>7115</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>20674</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>133085</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>126550</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>137363</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>94,67%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>90,03%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>118672</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>113646</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>121554</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>91,88%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>147500</t>
+          <t>116529</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139896</t>
+          <t>111304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>151630</t>
+          <t>119450</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
+          <t>95,66%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>249615</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>241678</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>254717</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>95,13%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>266172</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>258066</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>271625</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>427</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,92 +3136,92 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4888</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1268</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4556</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3234,74 +3234,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>156709</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>155074</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>127908</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>124267</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>137081</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>133800</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>137900</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,41%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>153648</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>151571</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>154159</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>384</t>
@@ -3309,27 +3309,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>281555</t>
+          <t>293789</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278267</t>
+          <t>290148</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>24904</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>664453</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>655166</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>672435</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>636580</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>628230</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>641959</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>720203</t>
+          <t>600959</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>709203</t>
+          <t>592983</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>728451</t>
+          <t>606975</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1356783</t>
+          <t>1265411</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1343607</t>
+          <t>1252529</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1367375</t>
+          <t>1275589</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
